--- a/1-任务资格判据手册与边界敏感性（数据表）.xlsx
+++ b/1-任务资格判据手册与边界敏感性（数据表）.xlsx
@@ -3835,7 +3835,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>R-A＋R-F：目标题即课堂同类导航编程任务的数字化版本（E2，含逐项材料），M/L 判 C；S 因无 E1 级逐题材料，按 Q-WP3-015 记 U</t>
+          <t>R-A＋R-F：目标题即课堂同类导航编程任务的数字化版本（E2，含逐项材料），M/L 判 C；S 因无 E1 级逐题材料，按 疑问编号 015 记 U</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>R-A＋R-F：目标题即课堂同类导航编程任务的数字化版本（E2，含逐项材料），M/L 判 C；S 因无 E1 级逐题材料，按 Q-WP3-015 记 U</t>
+          <t>R-A＋R-F：目标题即课堂同类导航编程任务的数字化版本（E2，含逐项材料），M/L 判 C；S 因无 E1 级逐题材料，按 疑问编号 015 记 U</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>**冻结判据（本版）**：本手册为**冻结件**，冻结的标准是**"操作核心完整、已知歧义已列名"**——**不是"内部无矛盾"**。歧义由裁定程序处理。**本版不设"由程序判定可否冻结"机制**（历轮证明该机制不可用：曾声称由 `_校验手册.py` 判定的三项检查从未实现）。</t>
+          <t>**冻结判据（本版）**：本手册为**冻结件**，冻结的标准是**"操作核心完整、已知歧义已列名"**——**不是"内部无矛盾"**。歧义按统一裁定口径处理。。</t>
         </is>
       </c>
     </row>
